--- a/Win32/Debug/RelatorioVendas.xlsx
+++ b/Win32/Debug/RelatorioVendas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bkp Robson\PROJROBSON\Loja2.0\Win32\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{356E0C8E-EE55-46CA-903C-04FF08D1905F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BB30EC9-BA50-4131-866A-A5F9F8C044B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1230" windowWidth="14400" windowHeight="10755" xr2:uid="{B02EC126-5361-405E-BF88-81FA308C03E0}"/>
+    <workbookView xWindow="1755" yWindow="1230" windowWidth="14400" windowHeight="10755" xr2:uid="{970C14C2-9FDF-49DB-AEBB-9A2BBDB0A7EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Relatório de Vendas</t>
   </si>
@@ -42,43 +42,25 @@
     <t>Valor Total</t>
   </si>
   <si>
-    <t>Cerveja</t>
-  </si>
-  <si>
-    <t>R$ 18,00</t>
-  </si>
-  <si>
     <t>teste</t>
   </si>
   <si>
+    <t>R$ 16,00</t>
+  </si>
+  <si>
     <t>R$ 32,00</t>
   </si>
   <si>
-    <t>Teste produto</t>
-  </si>
-  <si>
-    <t>R$ 50,50</t>
-  </si>
-  <si>
-    <t>Vult Facial</t>
-  </si>
-  <si>
-    <t>R$ 40,50</t>
-  </si>
-  <si>
-    <t>R$ 16,00</t>
-  </si>
-  <si>
     <t>R$ 48,00</t>
   </si>
   <si>
     <t>TOTAIS</t>
   </si>
   <si>
-    <t>Qtd. de Vendas: 8</t>
-  </si>
-  <si>
-    <t>R$ 269,00</t>
+    <t>Qtd. de Vendas: 3</t>
+  </si>
+  <si>
+    <t>R$ 96,00</t>
   </si>
 </sst>
 </file>
@@ -491,8 +473,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF8B1CC-BAF8-4B3E-8A04-F874E1782A94}">
-  <dimension ref="A1:D11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB1A7E9-DD45-49EE-9B93-A2E6C3D349F7}">
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -525,13 +507,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5">
-        <v>46359</v>
+        <v>46145</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -539,112 +521,42 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46145</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="5">
-        <v>46206</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5">
-        <v>46206</v>
+        <v>46145</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
-        <v>46176</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5">
-        <v>46176</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5">
-        <v>46145</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5">
-        <v>46145</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5">
-        <v>46145</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Win32/Debug/RelatorioVendas.xlsx
+++ b/Win32/Debug/RelatorioVendas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bkp Robson\PROJROBSON\Loja2.0\Win32\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BB30EC9-BA50-4131-866A-A5F9F8C044B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{019D5575-8AE2-4A8F-933A-5D552B1840B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1230" windowWidth="14400" windowHeight="10755" xr2:uid="{970C14C2-9FDF-49DB-AEBB-9A2BBDB0A7EE}"/>
+    <workbookView xWindow="1755" yWindow="1230" windowWidth="14400" windowHeight="10755" xr2:uid="{8471A29B-2B89-48C8-9ADA-ADE269D44B66}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Relatório de Vendas</t>
   </si>
@@ -42,25 +42,19 @@
     <t>Valor Total</t>
   </si>
   <si>
-    <t>teste</t>
-  </si>
-  <si>
-    <t>R$ 16,00</t>
-  </si>
-  <si>
-    <t>R$ 32,00</t>
-  </si>
-  <si>
-    <t>R$ 48,00</t>
+    <t>Cerveja</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>R$ 36,00</t>
   </si>
   <si>
     <t>TOTAIS</t>
   </si>
   <si>
-    <t>Qtd. de Vendas: 3</t>
-  </si>
-  <si>
-    <t>R$ 96,00</t>
+    <t>Qtd. de Vendas: 1</t>
   </si>
 </sst>
 </file>
@@ -132,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -144,9 +138,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -473,8 +464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB1A7E9-DD45-49EE-9B93-A2E6C3D349F7}">
-  <dimension ref="A1:D6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A359C0A7-A699-4AD0-A9B3-7E91E9373852}">
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -507,56 +498,28 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>7</v>
+        <v>1015</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
-        <v>46145</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5">
-        <v>46145</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5">
-        <v>46145</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Win32/Debug/RelatorioVendas.xlsx
+++ b/Win32/Debug/RelatorioVendas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bkp Robson\PROJROBSON\Loja2.0\Win32\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{019D5575-8AE2-4A8F-933A-5D552B1840B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB714CF1-85FE-44CC-B6A8-71868F6CF1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1230" windowWidth="14400" windowHeight="10755" xr2:uid="{8471A29B-2B89-48C8-9ADA-ADE269D44B66}"/>
+    <workbookView xWindow="1755" yWindow="1230" windowWidth="14400" windowHeight="10755" xr2:uid="{AE100E35-C731-42B5-BDF6-DE4AA4441B99}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
-  <si>
-    <t>Relatório de Vendas</t>
-  </si>
-  <si>
-    <t>Cód. Venda</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+  <si>
+    <t>Relatorio de Vendas</t>
+  </si>
+  <si>
+    <t>Cod. Venda</t>
   </si>
   <si>
     <t>Produto</t>
@@ -42,19 +42,76 @@
     <t>Valor Total</t>
   </si>
   <si>
+    <t>Vult Facial</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>R$ 99,00</t>
+  </si>
+  <si>
     <t>Cerveja</t>
   </si>
   <si>
+    <t>R$ 90,00</t>
+  </si>
+  <si>
+    <t>Produto Teste</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>R$ 57,98</t>
+  </si>
+  <si>
     <t>19/03/2026</t>
   </si>
   <si>
     <t>R$ 36,00</t>
   </si>
   <si>
+    <t>teste produto</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>R$ 1,00</t>
+  </si>
+  <si>
+    <t>R$ 18,00</t>
+  </si>
+  <si>
+    <t>teste</t>
+  </si>
+  <si>
+    <t>R$ 32,00</t>
+  </si>
+  <si>
+    <t>Teste produto</t>
+  </si>
+  <si>
+    <t>R$ 50,50</t>
+  </si>
+  <si>
+    <t>R$ 40,50</t>
+  </si>
+  <si>
+    <t>R$ 16,00</t>
+  </si>
+  <si>
+    <t>R$ 48,00</t>
+  </si>
+  <si>
     <t>TOTAIS</t>
   </si>
   <si>
-    <t>Qtd. de Vendas: 1</t>
+    <t>Qtd. de Vendas: 13</t>
+  </si>
+  <si>
+    <t>R$ 552,98</t>
   </si>
 </sst>
 </file>
@@ -126,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -142,6 +199,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -464,8 +524,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A359C0A7-A699-4AD0-A9B3-7E91E9373852}">
-  <dimension ref="A1:D4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9459F55-0961-436C-A46E-AC950F3203AA}">
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -498,7 +558,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -511,15 +571,183 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4">
+        <v>1018</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>1016</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>1015</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>1014</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6">
+        <v>46359</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="6">
+        <v>46206</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="6">
+        <v>46206</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="6">
+        <v>46176</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46176</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="6">
+        <v>46145</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46145</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="6">
+        <v>46145</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
